--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -1,37 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guideline_Profiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interpretations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derivations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLM_Verification" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDTM_Requirements" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Style" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Reconciliation" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioritisation" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Contract" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finding_Contract" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Integration" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extensibility" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Log" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Contents" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Definitions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Guideline_Profiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Interpretations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Derivations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Rules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Rule_Messages" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Approval" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GLM_Verification" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SDTM_Requirements" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Query_History" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Query_Style" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Confidence_Model" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Query_Reconciliation" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Prioritisation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Input_Contract" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Finding_Contract" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="LLM_Integration" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="API" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Testing" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Extensibility" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Open_Questions" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Traceability" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Review_Log" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$50</definedName>
@@ -232,7 +233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -254,11 +255,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00D9DED8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -436,6 +443,49 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -856,7 +906,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.5.0 — APPROVED, SDTM input requirements</t>
+          <t>2.6.0 — APPROVED, query history input contract</t>
         </is>
       </c>
     </row>
@@ -904,7 +954,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v2.4.0, issued 2026-08-22</t>
+          <t>v2.5.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1044,8 +1094,8 @@
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="A19:F19"/>
@@ -2511,7 +2561,6 @@
   <mergeCells count="16">
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B54:F54"/>
@@ -2524,6 +2573,7 @@
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2536,7 +2586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3981,6 +4031,7 @@
       </c>
       <c r="G45" s="26" t="inlineStr"/>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -4208,6 +4259,7 @@
       <c r="E58" s="26" t="inlineStr"/>
       <c r="F58" s="26" t="inlineStr"/>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
@@ -4275,12 +4327,25 @@
         </is>
       </c>
     </row>
+    <row r="66" ht="48" customHeight="1">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Preserve the EDC item-group sequence</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Added 2026-09-12 from TEA-CTR-004 finding 1. A Veeva query identifies a lesion only by the repeating form's Item Group Sequence Number; nothing else in the query export names a lesion. The conversion must therefore carry that sequence through to the tumour records — as a supplemental qualifier alongside TULNKID — or query history cannot be matched to a lesion finding, and every lesion query at a visit will suppress every lesion finding at that visit.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:F45"/>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B63:G63"/>
     <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B66:F66"/>
     <mergeCell ref="B65:G65"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B62:G62"/>
@@ -4291,6 +4356,2353 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Query history input contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="67" t="inlineStr">
+        <is>
+          <t>TEA-CTR-004. Derived column by column from a real Veeva EDC Query Detail export — study A101-1001_TST5, 69 queries, 54 columns, listing run 2026-09-12 11:40. Supplied by Daniel on 2026-09-12 with the warning that the format will change as Veeva releases new EDC versions, which is what adapter rules 1 to 4 are for. Feeds the query reconciliation model (OBJ-04) and the six TE-QM rules. Closes OI-09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Export column (Veeva header, verbatim)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Canonical field</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>R/C/O</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>In the 2026-09-12 export</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>What the agent does with it</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>If absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="68" t="inlineStr">
+        <is>
+          <t>Study</t>
+        </is>
+      </c>
+      <c r="B4" s="68" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="C4" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>A101-1001_TST5 — note the filename says A001-1001. The column wins; never parse the filename.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Checked against the study_id on the SDTM delivery before any rule runs. A query file from a different study is a wrong-data event, not a warning.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>site_id</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" s="72" t="inlineStr">
+        <is>
+          <t>5 sites across 4 countries.</t>
+        </is>
+      </c>
+      <c r="E5" s="72" t="inlineStr">
+        <is>
+          <t>Scopes the site-facing worklist and lets a reviewer see query load per site.</t>
+        </is>
+      </c>
+      <c r="F5" s="72" t="inlineStr">
+        <is>
+          <t>Matching still works on subject alone. The per-site view is lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="68" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B6" s="68" t="inlineStr">
+        <is>
+          <t>subject_id</t>
+        </is>
+      </c>
+      <c r="C6" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>23 subjects, e.g. A0019501001.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>The first matching key. Must be the same identifier as SDTM USUBJID, or mapped to it by a documented, reversible rule recorded in the run provenance.</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run. Reconciliation is impossible without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>Subject Status</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>subject_status</t>
+        </is>
+      </c>
+      <c r="C7" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D7" s="72" t="inlineStr">
+        <is>
+          <t>Enrolled, In Screening, Screen Failure.</t>
+        </is>
+      </c>
+      <c r="E7" s="72" t="inlineStr">
+        <is>
+          <t>Suppresses query aging on screen failures, which would otherwise accumulate TE-QM-004 findings nobody intends to action.</t>
+        </is>
+      </c>
+      <c r="F7" s="72" t="inlineStr">
+        <is>
+          <t>TE-QM-004 counts screen-failed subjects. Noise, not error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B8" s="68" t="inlineStr">
+        <is>
+          <t>site_country</t>
+        </is>
+      </c>
+      <c r="C8" s="74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Australia, South Korea, Spain, United States.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Evidence display only. Never used for matching.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>Event Group Label</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>visit_group</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" s="72" t="inlineStr">
+        <is>
+          <t>Screening only — this export covers one event group.</t>
+        </is>
+      </c>
+      <c r="E9" s="72" t="inlineStr">
+        <is>
+          <t>Second matching key with Event Label. Must reconcile to SDTM VISIT through the study visit map.</t>
+        </is>
+      </c>
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>Matching degrades to subject + field, which over-suppresses: a query on one visit can hide a finding on another.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>Event Label</t>
+        </is>
+      </c>
+      <c r="B10" s="68" t="inlineStr">
+        <is>
+          <t>visit_name</t>
+        </is>
+      </c>
+      <c r="C10" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Screening.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>The visit a query sits on. Together with Subject and Item OID this is the structural match.</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>Event Group Sequence Number</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>visit_occurrence</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" s="72" t="inlineStr">
+        <is>
+          <t>1 throughout.</t>
+        </is>
+      </c>
+      <c r="E11" s="72" t="inlineStr">
+        <is>
+          <t>Distinguishes repeating cycles. Required as soon as the study has a repeating event group, which every oncology tumour-assessment schedule does.</t>
+        </is>
+      </c>
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>Cycles collapse. A query on cycle 2 suppresses a finding on cycle 5. This is the most likely silent failure in the whole contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="68" t="inlineStr">
+        <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="B12" s="68" t="inlineStr">
+        <is>
+          <t>visit_date</t>
+        </is>
+      </c>
+      <c r="C12" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>10 distinct dates, ISO-8601 date only.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Confirms the query's visit is the visit the finding is on, where visit labels repeat.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to the visit label alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>Form Label</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>form_name</t>
+        </is>
+      </c>
+      <c r="C13" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" s="72" t="inlineStr">
+        <is>
+          <t>Essential Information.</t>
+        </is>
+      </c>
+      <c r="E13" s="72" t="inlineStr">
+        <is>
+          <t>Narrows to the CRF page. Needed where one visit carries several forms feeding the same SDTM domain.</t>
+        </is>
+      </c>
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>Matching degrades to visit + field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t>Form Sequence Number</t>
+        </is>
+      </c>
+      <c r="B14" s="68" t="inlineStr">
+        <is>
+          <t>form_occurrence</t>
+        </is>
+      </c>
+      <c r="C14" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1 throughout.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Repeating forms, in designs that put one form per lesion rather than one repeating group.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Same failure as Item Group Sequence Number, for those designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>Form Status</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>form_status</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D15" s="72" t="inlineStr">
+        <is>
+          <t>In Edit, Submitted.</t>
+        </is>
+      </c>
+      <c r="E15" s="72" t="inlineStr">
+        <is>
+          <t>Evidence only. A finding against an In Edit form is de-prioritised — the site has not finished with it.</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>Item Group Label</t>
+        </is>
+      </c>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>item_group</t>
+        </is>
+      </c>
+      <c r="C16" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Demographic Information, Enrollment Information.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Names the repeating group a query belongs to. With the sequence number, this is how a query reaches one specific lesion row.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Lesion-level matching is lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>Item Group Sequence Number</t>
+        </is>
+      </c>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>item_group_seq</t>
+        </is>
+      </c>
+      <c r="C17" s="70" t="inlineStr">
+        <is>
+          <t>R*</t>
+        </is>
+      </c>
+      <c r="D17" s="72" t="inlineStr">
+        <is>
+          <t>1 on every row — the forms in this sample do not repeat, so this export does not exercise the field at all.</t>
+        </is>
+      </c>
+      <c r="E17" s="72" t="inlineStr">
+        <is>
+          <t>THE LESION KEY. On a tumour form this is the repeating-row number, and it is the only thing in the export that says which lesion a query is about. TEA-CTR-003 must therefore preserve it through the SDTM conversion so it can be joined to TULNKID. See finding 1 below.</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>Every lesion query matches every lesion finding at that visit. Mass false suppression of real findings — the worst outcome the agent can produce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="68" t="inlineStr">
+        <is>
+          <t>Item OID</t>
+        </is>
+      </c>
+      <c r="B18" s="68" t="inlineStr">
+        <is>
+          <t>field_id</t>
+        </is>
+      </c>
+      <c r="C18" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>6 values: BRTHDAT, DMENDAT, DMSFREAS2, ETHNIC, LBSEX, RACE.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Third matching key. Mapped to the canonical evidence field names through a study-level field map maintained beside the visit map.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run. Structural matching is impossible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>Item Label</t>
+        </is>
+      </c>
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>field_label</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D19" s="72" t="inlineStr">
+        <is>
+          <t>One label per Item OID.</t>
+        </is>
+      </c>
+      <c r="E19" s="72" t="inlineStr">
+        <is>
+          <t>Evidence display, so a reviewer sees the question the site saw.</t>
+        </is>
+      </c>
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="68" t="inlineStr">
+        <is>
+          <t>Query ID</t>
+        </is>
+      </c>
+      <c r="B20" s="68" t="inlineStr">
+        <is>
+          <t>query_id</t>
+        </is>
+      </c>
+      <c r="C20" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>69 unique, VV-nnnnnn.</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>The stable handle shown to the reviewer and stored on the finding link. Also the dedupe key for the query side of reconciliation.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="70" t="inlineStr">
+        <is>
+          <t>Query Vault ID</t>
+        </is>
+      </c>
+      <c r="B21" s="70" t="inlineStr">
+        <is>
+          <t>query_uid</t>
+        </is>
+      </c>
+      <c r="C21" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D21" s="72" t="inlineStr">
+        <is>
+          <t>69 unique, OPW-prefixed.</t>
+        </is>
+      </c>
+      <c r="E21" s="72" t="inlineStr">
+        <is>
+          <t>Internal Vault key. Kept so a finding can be traced back to the EDC record during an audit.</t>
+        </is>
+      </c>
+      <c r="F21" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>Query Status</t>
+        </is>
+      </c>
+      <c r="B22" s="68" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Open (64) and Closed (5) ONLY. No Answered row appears — see finding 2.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Drives the entire reconciliation branch. Mapped through the status table below; an unrecognised value fails the run.</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="70" t="inlineStr">
+        <is>
+          <t>Restricted Query</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
+        <is>
+          <t>is_restricted</t>
+        </is>
+      </c>
+      <c r="C23" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D23" s="72" t="inlineStr">
+        <is>
+          <t>No on every row, although the filename is marked RESTRICTED.</t>
+        </is>
+      </c>
+      <c r="E23" s="72" t="inlineStr">
+        <is>
+          <t>A restricted query may carry access-controlled content. Restricted rows load as existence-only — id, status, scope and dates — with every free-text field dropped before the record leaves the adapter.</t>
+        </is>
+      </c>
+      <c r="F23" s="72" t="inlineStr">
+        <is>
+          <t>Treated as restricted. Failing safe costs some matching quality; failing open leaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="68" t="inlineStr">
+        <is>
+          <t>Query Team</t>
+        </is>
+      </c>
+      <c r="B24" s="68" t="inlineStr">
+        <is>
+          <t>owning_team</t>
+        </is>
+      </c>
+      <c r="C24" s="74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Data Management.</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Evidence and routing of the resulting finding.</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="70" t="inlineStr">
+        <is>
+          <t>Manual Query</t>
+        </is>
+      </c>
+      <c r="B25" s="70" t="inlineStr">
+        <is>
+          <t>is_manual</t>
+        </is>
+      </c>
+      <c r="C25" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D25" s="72" t="inlineStr">
+        <is>
+          <t>No on every row — all 69 are system edit checks.</t>
+        </is>
+      </c>
+      <c r="E25" s="72" t="inlineStr">
+        <is>
+          <t>Separates EDC edit checks from human queries. Only a manual query carries a person's reasoning, and only a manual query can be one TEA itself raised.</t>
+        </is>
+      </c>
+      <c r="F25" s="72" t="inlineStr">
+        <is>
+          <t>Everything is treated as manual, which weakens the TEA-origin test and sends system query text to the model needlessly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="68" t="inlineStr">
+        <is>
+          <t>Query Rule</t>
+        </is>
+      </c>
+      <c r="B26" s="68" t="inlineStr">
+        <is>
+          <t>source_rule_id</t>
+        </is>
+      </c>
+      <c r="C26" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>6 values: DM_002, DM_003, DM_007, DM_008, DM_010, R_QUERY_DMENDAT_FD.</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Two jobs. (a) Exact-match key for a query TEA itself raised: TEA writes its TE- rule id here. (b) Tells the agent an EDC edit check already covers a field, so it does not duplicate the sponsor's own programming.</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Exact matching degrades to structural and semantic only, and TEA cannot recognise its own prior queries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="70" t="inlineStr">
+        <is>
+          <t>Number of Query Messages</t>
+        </is>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
+          <t>message_count</t>
+        </is>
+      </c>
+      <c r="C27" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D27" s="72" t="inlineStr">
+        <is>
+          <t>1 on every open row, 2 on every closed row.</t>
+        </is>
+      </c>
+      <c r="E27" s="72" t="inlineStr">
+        <is>
+          <t>A thread with more than two messages contains a conversation and is flagged for a human look regardless of the automated assessment.</t>
+        </is>
+      </c>
+      <c r="F27" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="68" t="inlineStr">
+        <is>
+          <t>Days Unresolved</t>
+        </is>
+      </c>
+      <c r="B28" s="68" t="inlineStr">
+        <is>
+          <t>(deliberately not mapped)</t>
+        </is>
+      </c>
+      <c r="C28" s="77" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Open rows = listing date − created. Closed rows = closed − created. Exactly reproducible from the other columns.</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DO NOT USE. It is computed against Last Run of Listing, not against the agent's data-cut date. TE-QM-004 recomputes aging from Query Created Date against the run's as-of date. See finding 5.</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>n/a — the agent never reads it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="70" t="inlineStr">
+        <is>
+          <t>Original Query Text</t>
+        </is>
+      </c>
+      <c r="B29" s="70" t="inlineStr">
+        <is>
+          <t>query_text</t>
+        </is>
+      </c>
+      <c r="C29" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D29" s="72" t="inlineStr">
+        <is>
+          <t>4 distinct system-generated texts.</t>
+        </is>
+      </c>
+      <c r="E29" s="72" t="inlineStr">
+        <is>
+          <t>Input to P-MATCH-QUERY and P-ASSESS-ANSWER, inside the untrusted-data envelope (DP-07).</t>
+        </is>
+      </c>
+      <c r="F29" s="72" t="inlineStr">
+        <is>
+          <t>Semantic matching deactivates. Exact and structural matching still work, so the run continues degraded rather than failing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="68" t="inlineStr">
+        <is>
+          <t>Original Query Text in English</t>
+        </is>
+      </c>
+      <c r="B30" s="68" t="inlineStr">
+        <is>
+          <t>query_text_en</t>
+        </is>
+      </c>
+      <c r="C30" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Identical to Original Query Text here — this study runs in English.</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>The column the model actually reads, so a query raised in the site's language is still assessable by GLM v5.2.</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to Original Query Text, and a non-English query then reaches the model in its own language.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="70" t="inlineStr">
+        <is>
+          <t>Original Query Text in the Base Language</t>
+        </is>
+      </c>
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>query_text_base</t>
+        </is>
+      </c>
+      <c r="C31" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D31" s="72" t="inlineStr">
+        <is>
+          <t>Identical to Original Query Text here.</t>
+        </is>
+      </c>
+      <c r="E31" s="72" t="inlineStr">
+        <is>
+          <t>Shown to the reviewer when the study base language is not English.</t>
+        </is>
+      </c>
+      <c r="F31" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to Original Query Text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="68" t="inlineStr">
+        <is>
+          <t>Latest Query Comment</t>
+        </is>
+      </c>
+      <c r="B32" s="68" t="inlineStr">
+        <is>
+          <t>latest_message_text</t>
+        </is>
+      </c>
+      <c r="C32" s="74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>A COPY of the original query text on 64 rows; blank on all 5 closed rows.</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>TRAP — this is not the site's answer. It is the most recent message on the thread, which for a system query is the query itself. It must never be passed to P-ASSESS-ANSWER. Carried for display only. See finding 3.</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="70" t="inlineStr">
+        <is>
+          <t>Latest Query Answer Text</t>
+        </is>
+      </c>
+      <c r="B33" s="70" t="inlineStr">
+        <is>
+          <t>answer_text</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D33" s="72" t="inlineStr">
+        <is>
+          <t>EMPTY on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E33" s="72" t="inlineStr">
+        <is>
+          <t>The only field carrying the site's reply, and the sole input to P-ASSESS-ANSWER and so to TE-QM-002 and TE-QM-005.</t>
+        </is>
+      </c>
+      <c r="F33" s="72" t="inlineStr">
+        <is>
+          <t>JUSTIFIED_BY_ANSWER becomes unreachable. Every closed query whose finding still evaluates true becomes ANSWERED_UNRESOLVED and is surfaced. Safe, but noisier — and it means the answer path is untested. See finding 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="68" t="inlineStr">
+        <is>
+          <t>Item Value Changed</t>
+        </is>
+      </c>
+      <c r="B34" s="68" t="inlineStr">
+        <is>
+          <t>value_changed</t>
+        </is>
+      </c>
+      <c r="C34" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Yes on 4 rows, No on 65.</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>DETERMINISTIC answer to 'was the data actually corrected?'. Removes the model from part of TE-QM-002 and from all of TE-QM-006. See finding 4.</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to comparing the current SDTM value against the finding — weaker, and unavailable for any EDC field SDTM does not carry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="70" t="inlineStr">
+        <is>
+          <t>Query Caused Data Change</t>
+        </is>
+      </c>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>change_attributed_to_query</t>
+        </is>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" s="72" t="inlineStr">
+        <is>
+          <t>Identical to Item Value Changed on all 69 rows, so this export cannot show the two diverging.</t>
+        </is>
+      </c>
+      <c r="E35" s="72" t="inlineStr">
+        <is>
+          <t>Separates a correction made in response to the query from an unrelated edit that happened to land on the same field. TE-QM-006 needs the distinction.</t>
+        </is>
+      </c>
+      <c r="F35" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to Item Value Changed alone, which over-credits the query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="68" t="inlineStr">
+        <is>
+          <t>Item Value Before Query</t>
+        </is>
+      </c>
+      <c r="B36" s="68" t="inlineStr">
+        <is>
+          <t>value_before</t>
+        </is>
+      </c>
+      <c r="C36" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Populated only on the 4 changed rows. PERSONAL DATA — three of the four are birth years.</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Evidence: shows the reviewer what was corrected. Redacted by guardrail G-06 before any prompt is assembled. See finding 6.</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Evidence display loses the before value; no rule is affected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="70" t="inlineStr">
+        <is>
+          <t>Item Value Now</t>
+        </is>
+      </c>
+      <c r="B37" s="70" t="inlineStr">
+        <is>
+          <t>value_after</t>
+        </is>
+      </c>
+      <c r="C37" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D37" s="72" t="inlineStr">
+        <is>
+          <t>Populated only on the 4 changed rows.</t>
+        </is>
+      </c>
+      <c r="E37" s="72" t="inlineStr">
+        <is>
+          <t>Cross-checked against the SDTM value for the same field. A mismatch means the query export and the SDTM cut are not from the same point in time, which invalidates every reconciliation outcome in the run.</t>
+        </is>
+      </c>
+      <c r="F37" s="72" t="inlineStr">
+        <is>
+          <t>The cut-alignment check deactivates and a stale query file goes undetected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="68" t="inlineStr">
+        <is>
+          <t>Value Confirmed</t>
+        </is>
+      </c>
+      <c r="B38" s="68" t="inlineStr">
+        <is>
+          <t>value_confirmed</t>
+        </is>
+      </c>
+      <c r="C38" s="74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Site confirmed the value as correct without changing it. Direct, non-LLM evidence for JUSTIFIED_BY_ANSWER where it is populated.</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to assessing the answer text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="70" t="inlineStr">
+        <is>
+          <t>Observed Source Value</t>
+        </is>
+      </c>
+      <c r="B39" s="70" t="inlineStr">
+        <is>
+          <t>source_value</t>
+        </is>
+      </c>
+      <c r="C39" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D39" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E39" s="72" t="inlineStr">
+        <is>
+          <t>Source-data-verification value. Not used by any rule.</t>
+        </is>
+      </c>
+      <c r="F39" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="68" t="inlineStr">
+        <is>
+          <t>Query Created Date</t>
+        </is>
+      </c>
+      <c r="B40" s="68" t="inlineStr">
+        <is>
+          <t>opened_at</t>
+        </is>
+      </c>
+      <c r="C40" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>ISO-8601 UTC to the minute, e.g. 2026-01-17T01:04Z. Range 2026-01-17 to 2026-07-01.</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Aging (TE-QM-004, recomputed — see Days Unresolved) and the ordering that the recurrence test depends on.</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="70" t="inlineStr">
+        <is>
+          <t>Query Created By</t>
+        </is>
+      </c>
+      <c r="B41" s="70" t="inlineStr">
+        <is>
+          <t>opened_by</t>
+        </is>
+      </c>
+      <c r="C41" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D41" s="72" t="inlineStr">
+        <is>
+          <t>System on every row.</t>
+        </is>
+      </c>
+      <c r="E41" s="72" t="inlineStr">
+        <is>
+          <t>Evidence, and a cross-check on Manual Query.</t>
+        </is>
+      </c>
+      <c r="F41" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="68" t="inlineStr">
+        <is>
+          <t>Created By Query Team</t>
+        </is>
+      </c>
+      <c r="B42" s="68" t="inlineStr">
+        <is>
+          <t>opened_by_team</t>
+        </is>
+      </c>
+      <c r="C42" s="74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Data Management.</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Evidence.</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="70" t="inlineStr">
+        <is>
+          <t>Created By Role</t>
+        </is>
+      </c>
+      <c r="B43" s="70" t="inlineStr">
+        <is>
+          <t>opened_by_role</t>
+        </is>
+      </c>
+      <c r="C43" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D43" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E43" s="72" t="inlineStr">
+        <is>
+          <t>Evidence.</t>
+        </is>
+      </c>
+      <c r="F43" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="68" t="inlineStr">
+        <is>
+          <t>Query Answered Date</t>
+        </is>
+      </c>
+      <c r="B44" s="68" t="inlineStr">
+        <is>
+          <t>answered_at</t>
+        </is>
+      </c>
+      <c r="C44" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>EMPTY on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Orders the thread, and tells the agent whether the site's answer preceded or followed the data change — which is what separates 'corrected as promised' from 'corrected, then explained away'.</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Answer ordering falls back to the closed date, losing that distinction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="70" t="inlineStr">
+        <is>
+          <t>Query Answered By</t>
+        </is>
+      </c>
+      <c r="B45" s="70" t="inlineStr">
+        <is>
+          <t>answered_by</t>
+        </is>
+      </c>
+      <c r="C45" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D45" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E45" s="72" t="inlineStr">
+        <is>
+          <t>Evidence.</t>
+        </is>
+      </c>
+      <c r="F45" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t>Answered By Role</t>
+        </is>
+      </c>
+      <c r="B46" s="68" t="inlineStr">
+        <is>
+          <t>answered_by_role</t>
+        </is>
+      </c>
+      <c r="C46" s="74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Evidence. Would distinguish an investigator's answer from a study coordinator's, which matters for a medical judgement.</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>No effect on any rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="70" t="inlineStr">
+        <is>
+          <t>Answered By Query Team</t>
+        </is>
+      </c>
+      <c r="B47" s="70" t="inlineStr">
+        <is>
+          <t>answered_by_team</t>
+        </is>
+      </c>
+      <c r="C47" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D47" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E47" s="72" t="inlineStr">
+        <is>
+          <t>Evidence.</t>
+        </is>
+      </c>
+      <c r="F47" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="68" t="inlineStr">
+        <is>
+          <t>Query Closed Date</t>
+        </is>
+      </c>
+      <c r="B48" s="68" t="inlineStr">
+        <is>
+          <t>closed_at</t>
+        </is>
+      </c>
+      <c r="C48" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Populated on the 5 closed rows.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Required whenever status is Closed. Feeds the RECURRENT test and the aging recomputation.</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Recurrence detection degrades to run-to-run comparison only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="70" t="inlineStr">
+        <is>
+          <t>Query Closed By</t>
+        </is>
+      </c>
+      <c r="B49" s="70" t="inlineStr">
+        <is>
+          <t>closed_by</t>
+        </is>
+      </c>
+      <c r="C49" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D49" s="72" t="inlineStr">
+        <is>
+          <t>System on all 5 closed rows.</t>
+        </is>
+      </c>
+      <c r="E49" s="72" t="inlineStr">
+        <is>
+          <t>A close by System is an auto-close triggered by the data change, NOT a site-accepted resolution. The agent must not read it as agreement. Where the closer is a person, the close carries more weight.</t>
+        </is>
+      </c>
+      <c r="F49" s="72" t="inlineStr">
+        <is>
+          <t>The auto-close signal is lost and a system close is treated as a human one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="68" t="inlineStr">
+        <is>
+          <t>Closed By Query Team</t>
+        </is>
+      </c>
+      <c r="B50" s="68" t="inlineStr">
+        <is>
+          <t>closed_by_team</t>
+        </is>
+      </c>
+      <c r="C50" s="74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Data Management on the 5 closed rows.</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Evidence.</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="70" t="inlineStr">
+        <is>
+          <t>Closed By Role</t>
+        </is>
+      </c>
+      <c r="B51" s="70" t="inlineStr">
+        <is>
+          <t>closed_by_role</t>
+        </is>
+      </c>
+      <c r="C51" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D51" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E51" s="72" t="inlineStr">
+        <is>
+          <t>Evidence.</t>
+        </is>
+      </c>
+      <c r="F51" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="68" t="inlineStr">
+        <is>
+          <t>Last Run of Listing</t>
+        </is>
+      </c>
+      <c r="B52" s="68" t="inlineStr">
+        <is>
+          <t>export_as_of</t>
+        </is>
+      </c>
+      <c r="C52" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:40 on every row. No timezone in the value; the filename says KST. See finding 5.</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>The as-of timestamp of the query file. Compared against the SDTM cut date: a gap beyond the configured tolerance warns, because a stale query file manufactures false NEW findings. Enters the run provenance with the file's SHA-256.</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Fail the run. A query file with no as-of date cannot be safely reconciled against a data cut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="70" t="inlineStr">
+        <is>
+          <t>Visit Method</t>
+        </is>
+      </c>
+      <c r="B53" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="78" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D53" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E53" s="72" t="inlineStr">
+        <is>
+          <t>Not used. On-site versus remote visit; no rule depends on it.</t>
+        </is>
+      </c>
+      <c r="F53" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="68" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B54" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C54" s="77" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Reserved for externally sourced data (e.g. a lab feed). Not used.</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="70" t="inlineStr">
+        <is>
+          <t>Source System Name</t>
+        </is>
+      </c>
+      <c r="B55" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" s="78" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D55" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E55" s="72" t="inlineStr">
+        <is>
+          <t>Not used.</t>
+        </is>
+      </c>
+      <c r="F55" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="68" t="inlineStr">
+        <is>
+          <t>Source User</t>
+        </is>
+      </c>
+      <c r="B56" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C56" s="77" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Not used.</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="70" t="inlineStr">
+        <is>
+          <t>Source ID</t>
+        </is>
+      </c>
+      <c r="B57" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C57" s="78" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D57" s="72" t="inlineStr">
+        <is>
+          <t>Empty on all 69 rows.</t>
+        </is>
+      </c>
+      <c r="E57" s="72" t="inlineStr">
+        <is>
+          <t>Not used.</t>
+        </is>
+      </c>
+      <c r="F57" s="72" t="inlineStr">
+        <is>
+          <t>No effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="79" t="inlineStr">
+        <is>
+          <t>R = required, the run fails without it.   C = conditional, its absence deactivates a named behaviour and is reported.   O = optional, evidence only.   – = present in the export and deliberately not used.   R* = required for lesion-level data specifically; see finding 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Query status vocabulary</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Veeva value</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Canonical status</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>In this export</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Reconciliation branch</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Confirmed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="41.5" customHeight="1">
+      <c r="A63" s="68" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="B63" s="68" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>64 of 69</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>DUPLICATE_OPEN. The finding is linked to the query and suppressed from the default worklist. TE-QM-001 records it; TE-QM-004 ages it.</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Confirmed by this export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="66.5" customHeight="1">
+      <c r="A64" s="70" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B64" s="70" t="inlineStr">
+        <is>
+          <t>ANSWERED</t>
+        </is>
+      </c>
+      <c r="C64" s="72" t="inlineStr">
+        <is>
+          <t>0 — never appears</t>
+        </is>
+      </c>
+      <c r="D64" s="80" t="n"/>
+      <c r="E64" s="72" t="inlineStr">
+        <is>
+          <t>Answer-assessment branch: P-ASSESS-ANSWER runs and TE-QM-002 / TE-QM-005 apply.</t>
+        </is>
+      </c>
+      <c r="F64" s="72" t="inlineStr">
+        <is>
+          <t>NOT confirmed. The value is assumed from the Veeva data model and must be verified against an export that contains site-answered queries before Step 3 closes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="66.5" customHeight="1">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B65" s="68" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>5 of 69</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Answer-assessment branch, with one deterministic short-circuit: where Query Closed By is System AND Query Caused Data Change is Yes, the close is an auto-close on correction. The outcome is RESOLVED_BY_CORRECTION and the model is not called at all.</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Confirmed by this export — all 5 closed rows are exactly this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="66.5" customHeight="1">
+      <c r="A66" s="70" t="inlineStr">
+        <is>
+          <t>Cancelled, or any other value</t>
+        </is>
+      </c>
+      <c r="B66" s="70" t="inlineStr">
+        <is>
+          <t>— (no mapping)</t>
+        </is>
+      </c>
+      <c r="C66" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D66" s="80" t="n"/>
+      <c r="E66" s="72" t="inlineStr">
+        <is>
+          <t>The run fails before any rule executes, naming the column, the value and the affected Query IDs.</t>
+        </is>
+      </c>
+      <c r="F66" s="72" t="inlineStr">
+        <is>
+          <t>Deliberate. These vocabularies are small and stable; a new value is a specification event, not something to guess at. See adapter rule 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Adapter rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="41.5" customHeight="1">
+      <c r="A70" s="68" t="inlineStr">
+        <is>
+          <t>1. Bind by column name, never by position.</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>The export is a flat CSV with a header row and no BOM (ASCII in this sample; read as UTF-8 with a BOM tolerated). Column order is not part of the contract and a future EDC version is free to change it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="41.5" customHeight="1">
+      <c r="A71" s="70" t="inlineStr">
+        <is>
+          <t>2. Match header names leniently, values strictly.</t>
+        </is>
+      </c>
+      <c r="B71" s="80" t="n"/>
+      <c r="C71" s="72" t="inlineStr">
+        <is>
+          <t>Header matching trims surrounding whitespace, collapses internal runs of spaces and ignores case. Everything after that — controlled values, date formats — is matched exactly.</t>
+        </is>
+      </c>
+      <c r="D71" s="80" t="n"/>
+      <c r="E71" s="80" t="n"/>
+      <c r="F71" s="80" t="n"/>
+    </row>
+    <row r="72" ht="41.5" customHeight="1">
+      <c r="A72" s="68" t="inlineStr">
+        <is>
+          <t>3. Ignore columns the adapter does not know, and list them in the run log.</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>This is what lets a new EDC version add columns without breaking a validated run. Silently dropping them would be worse: the log entry is how anyone notices there is new information available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="41.5" customHeight="1">
+      <c r="A73" s="70" t="inlineStr">
+        <is>
+          <t>4. Fail the run on a missing R column, before any rule executes.</t>
+        </is>
+      </c>
+      <c r="B73" s="80" t="n"/>
+      <c r="C73" s="72" t="inlineStr">
+        <is>
+          <t>Naming the column. A partial reconciliation is more dangerous than none, because a missing key produces false suppressions that look like a clean data set.</t>
+        </is>
+      </c>
+      <c r="D73" s="80" t="n"/>
+      <c r="E73" s="80" t="n"/>
+      <c r="F73" s="80" t="n"/>
+    </row>
+    <row r="74" ht="41.5" customHeight="1">
+      <c r="A74" s="68" t="inlineStr">
+        <is>
+          <t>5. Deactivate, report and continue on a missing C column.</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>The dependent behaviour switches off and says so on the coverage report. Never silently — 'if absent' in the table above is the reviewer-facing text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="54" customHeight="1">
+      <c r="A75" s="70" t="inlineStr">
+        <is>
+          <t>6. Fail the run on an unrecognised value in a controlled column.</t>
+        </is>
+      </c>
+      <c r="B75" s="80" t="n"/>
+      <c r="C75" s="72" t="inlineStr">
+        <is>
+          <t>Query Status, Manual Query, Restricted Query, Item Value Changed and Query Caused Data Change. An operational override exists for an urgent cut: it maps the unknown value to OPEN_UNRECOGNISED, suppresses nothing, and marks every affected finding unreconciled. The override is off by default and is recorded in the run provenance.</t>
+        </is>
+      </c>
+      <c r="D75" s="80" t="n"/>
+      <c r="E75" s="80" t="n"/>
+      <c r="F75" s="80" t="n"/>
+    </row>
+    <row r="76" ht="41.5" customHeight="1">
+      <c r="A76" s="68" t="inlineStr">
+        <is>
+          <t>7. Empty is unknown, not false.</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>A blank Yes/No cell must not become False. Five of these columns are entirely empty in this export, and treating blank as No would have silently asserted things the file never said.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="29" customHeight="1">
+      <c r="A77" s="70" t="inlineStr">
+        <is>
+          <t>8. Never parse the filename.</t>
+        </is>
+      </c>
+      <c r="B77" s="80" t="n"/>
+      <c r="C77" s="72" t="inlineStr">
+        <is>
+          <t>The filename in this sample says A001-1001 while the Study column says A101-1001_TST5. The columns are the contract; the filename is not.</t>
+        </is>
+      </c>
+      <c r="D77" s="80" t="n"/>
+      <c r="E77" s="80" t="n"/>
+      <c r="F77" s="80" t="n"/>
+    </row>
+    <row r="78" ht="41.5" customHeight="1">
+      <c r="A78" s="68" t="inlineStr">
+        <is>
+          <t>9. Stamp the run with the adapter version, the file SHA-256 and Last Run of Listing.</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Reconciliation outcomes are only reproducible if the exact query file is identifiable. This is an ALCOA+ requirement, not a convenience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="41.5" customHeight="1">
+      <c r="A79" s="70" t="inlineStr">
+        <is>
+          <t>10. Treat every text field as untrusted input (DP-07).</t>
+        </is>
+      </c>
+      <c r="B79" s="80" t="n"/>
+      <c r="C79" s="72" t="inlineStr">
+        <is>
+          <t>Query text, comments and answers originate outside the trust boundary. They are passed to GLM v5.2 inside an explicit data envelope, with instruction-like content flagged, and they can never alter a deterministic verdict.</t>
+        </is>
+      </c>
+      <c r="D79" s="80" t="n"/>
+      <c r="E79" s="80" t="n"/>
+      <c r="F79" s="80" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>What the real export changed, and what it could not tell us</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Detail and consequence</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="91.5" customHeight="1">
+      <c r="A83" s="68" t="inlineStr">
+        <is>
+          <t>1. Nothing in the export identifies a lesion.</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>A query points at (subject, visit, form, item group sequence, item OID). There is no lesion id. For a repeating tumour form, Item Group Sequence Number is the ONLY thing that says which lesion row a query sits on — and in this export it is 1 on every row, because the forms sampled do not repeat, so the mechanism is entirely untested. Consequence for TEA-CTR-003: the SDTM conversion must preserve the EDC item-group sequence alongside TULNKID, or lesion-level query matching is impossible and every lesion query at a visit will suppress every lesion finding at that visit. Added to the SDTM requirements as a conversion obligation.</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>ACTION — confirm with clinical programming that the sequence survives the conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="79" customHeight="1">
+      <c r="A84" s="70" t="inlineStr">
+        <is>
+          <t>2. This export contains no site answers at all, so the answer path is unexercised.</t>
+        </is>
+      </c>
+      <c r="B84" s="80" t="n"/>
+      <c r="C84" s="72" t="inlineStr">
+        <is>
+          <t>Latest Query Answer Text, Query Answered Date, Query Answered By, Answered By Role and Answered By Query Team are empty on all 69 rows, and no row carries status Answered. All 69 are system edit checks (Manual Query = No, Query Created By = System) and the 5 closed ones were auto-closed on data change. P-ASSESS-ANSWER, TE-QM-002 and TE-QM-005 — the LLM-adjudicated part of the query model — therefore have no example to build or test against. Two possibilities need separating: this listing does not populate the answer columns, or this study genuinely has no answered queries yet.</t>
+        </is>
+      </c>
+      <c r="D84" s="80" t="n"/>
+      <c r="E84" s="80" t="n"/>
+      <c r="F84" s="72" t="inlineStr">
+        <is>
+          <t>ACTION — a second export containing manual, site-answered queries is needed before Step 3 can test the answer path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="66.5" customHeight="1">
+      <c r="A85" s="68" t="inlineStr">
+        <is>
+          <t>3. Latest Query Comment is not the answer, and looks exactly like one.</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>On 64 of 69 rows it is a verbatim copy of Original Query Text, and it is blank on every closed row. It is the latest message on the thread, which for a system query is the query itself. An implementation that reaches for the obviously-named field would feed the agent's own query text to P-ASSESS-ANSWER as if it were the site's reply, and the model would dutifully assess it. Recorded here so the adapter is written against the real semantics.</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>CLOSED by this contract — the field is display-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="116.5" customHeight="1">
+      <c r="A86" s="70" t="inlineStr">
+        <is>
+          <t>4. Part of TE-QM-002 becomes deterministic.</t>
+        </is>
+      </c>
+      <c r="B86" s="80" t="n"/>
+      <c r="C86" s="72" t="inlineStr">
+        <is>
+          <t>Item Value Changed and Query Caused Data Change answer 'was the data actually corrected, and because of this query?' as a fact carried by the EDC, in a single cut. The approved design assumed this needed either LLM judgement (TE-QM-002) or a run-to-run diff (TE-QM-006). Under DP-01 the deterministic answer must win: where these columns are present, the correction fact is read, not inferred, and the model is asked only the question it is actually needed for — whether the site's reasoning justifies data that was NOT corrected. TE-QM-006 loses its two-run dependency entirely.</t>
+        </is>
+      </c>
+      <c r="D86" s="80" t="n"/>
+      <c r="E86" s="80" t="n"/>
+      <c r="F86" s="72" t="inlineStr">
+        <is>
+          <t>CHANGE CONTROL — the rule pack is FROZEN at 2.0.0 and no rule text, message or base rate is changed here. This is recorded as a proposed implementation refinement, to be confirmed with evidence at the Step 3 gate and taken through rule change control at that point if it alters the stated logic of TE-QM-002 or TE-QM-006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="91.5" customHeight="1">
+      <c r="A87" s="68" t="inlineStr">
+        <is>
+          <t>5. Days Unresolved is measured against the export, not against the data cut.</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>It is exactly reproducible: closed − created for closed rows, listing date − created for open ones. In this sample the open rows read 73 to 221 days because the listing ran on 12 September, months after the queries opened. If the query file and the SDTM cut are from different dates — which is normal, they are pulled separately — an aging rule that trusts this column measures from the wrong reference. TE-QM-004 recomputes from Query Created Date against the run's as-of date. Separately, Last Run of Listing carries no timezone in the value while the filename says KST; the adapter requires the timezone as configuration and records it in the provenance.</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>CLOSED by this contract — the column is not mapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="79" customHeight="1">
+      <c r="A88" s="70" t="inlineStr">
+        <is>
+          <t>6. The query export carries personal data in fields nobody would look for it in.</t>
+        </is>
+      </c>
+      <c r="B88" s="80" t="n"/>
+      <c r="C88" s="72" t="inlineStr">
+        <is>
+          <t>Item Value Before Query and Item Value Now hold the raw field values, and in this sample three of the four are birth years (2008 → 1989, 1910 → 1951, 1906 → 1953). The file also carries site and subject identifiers throughout, and is marked RESTRICTED in its filename while Restricted Query reads No on every row. Guardrail G-06 was scoped for tumour data. It is extended to the query-history block: value_before and value_after are redacted before any prompt is assembled, and the file is handled at the same sensitivity as the clinical data set.</t>
+        </is>
+      </c>
+      <c r="D88" s="80" t="n"/>
+      <c r="E88" s="80" t="n"/>
+      <c r="F88" s="72" t="inlineStr">
+        <is>
+          <t>CLOSED by this contract — G-06 extended, and the Restricted Query flag alone is not treated as sufficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>How to use this while the agent is being built</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="48" customHeight="1">
+      <c r="A91" s="30" t="inlineStr">
+        <is>
+          <t>Build the dummy query file to this sheet</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>The synthetic study needs a query export with exactly these column names, and it must contain what this one does not: manual queries, site-answered queries, a query on a repeating lesion row, and a closed query whose value was NOT changed. Those four cases are the ones the approved reconciliation model turns on and the ones this export cannot test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>Reconciliation is a documented degradation, not a switch</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Missing C columns take capability away one behaviour at a time, and every run states which. That is the same posture as the SDTM coverage report and it exists so a reviewer is never shown a quiet worklist that is quiet because the inputs were thin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="30" t="inlineStr">
+        <is>
+          <t>The contract survives the EDC version changing</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Daniel's note with this export is that the format will change with future Veeva releases. Adapter rules 1 to 4 are the response: bind by name, tolerate additions, fail loudly on removals. When a new export arrives, re-run the profile and diff it against this sheet before changing any code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>Query history is not optional in practice</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>TEA-CTR-001 marks the queries block not required, and that stays true — the agent runs without it. But without it every finding is NEW, the agent re-raises what the study team already asked, and OBJ-04 is unmet. Treat it as required for any real data cut.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="48">
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C76:F76"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4614,7 +7026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4651,7 +7063,7 @@
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>confidence = clamp(
     rule.confidence_base_rate
@@ -4940,13 +7352,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4965,7 +7377,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>AMENDED at review (OBJ-04).</t>
+          <t>AMENDED at review (OBJ-04). Input contract: Query_History (TEA-CTR-004), derived from a real Veeva export on 2026-09-12.</t>
         </is>
       </c>
     </row>
@@ -4977,7 +7389,7 @@
       </c>
     </row>
     <row r="4" ht="330" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>for each candidate finding f:
     exact      = queries where tea_rule_id == f.rule_id and subject matches and scope overlaps
@@ -5051,6 +7463,27 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>•  The correction fact is read, not inferred. Where the export carries Item Value Changed and Query Caused Data Change, 'was the data corrected in response to this query?' is answered deterministically and the model is never asked it (DP-01). A query closed by System with a caused data change resolves to RESOLVED_BY_CORRECTION with no LLM call. The model is asked only whether an answer justifies data that was NOT corrected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>•  Only Latest Query Answer Text is an answer. Latest Query Comment is the newest message on the thread — for a system query, a copy of the query itself — and is never passed to P-ASSESS-ANSWER. See Query_History finding 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>•  Aging is recomputed, never read. The export's Days Unresolved is measured against the export's own listing date, so TE-QM-004 derives it from Query Created Date against the run's as-of date. A query file whose as-of date is outside tolerance of the SDTM cut warns before rules run.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
@@ -5061,7 +7494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5091,7 +7524,7 @@
       </c>
     </row>
     <row r="4" ht="130" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>Root-cause ordering within a subject:
   ST &gt; BL &gt; FU &gt; RS/IR &gt; XD
@@ -5114,7 +7547,7 @@
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>priority_score = severity_weight       # CRITICAL 100, MAJOR 40, MINOR 10, INFO 2
                * endpoint_impact       # 1.5 if it changes a derived response, progression date
@@ -5141,7 +7574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5167,7 +7600,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>TEA-CTR-001. Veeva EDC export is the primary profile; SDTM secondary. Source adapters produce this; rules never see source field names.</t>
+          <t>TEA-CTR-001. SDTM is the primary source profile (OQ-01, reversed 2026-08-22); the Veeva EDC export profile is retained for the in-company deployment. Source adapters produce this; rules never see source field names.</t>
         </is>
       </c>
     </row>
@@ -5437,7 +7870,7 @@
       </c>
       <c r="B13" s="66" t="inlineStr">
         <is>
-          <t>query_id, query_text, answer_text, status, opened/answered/closed dates, tea_rule_id</t>
+          <t>query_id, query_text, answer_text, status, opened/answered/closed dates, source_rule_id, item_group_seq, value_changed, change_attributed_to_query, export_as_of</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
@@ -5452,7 +7885,7 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Veeva query report. Absent means every finding is NEW</t>
+          <t>Veeva EDC Query Detail export. See Query_History (TEA-CTR-004) for the column-by-column contract. Formally optional — absent, every finding is NEW — but required in practice for any real data cut, or the agent re-raises what the study team already asked.</t>
         </is>
       </c>
     </row>
@@ -5581,7 +8014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6125,442 +8558,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Model integration contract</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Prompt contracts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Inputs</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Output schema</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>P-ADJ-NONMEASURABLE</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>adjudicate</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Lesion organ, laterality, location text, description text, method, guideline extract</t>
-        </is>
-      </c>
-      <c r="D5" s="65" t="inlineStr">
-        <is>
-          <t>{is_non_measurable, category, confidence, rationale}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>P-ADJ-UNEQUIVOCAL</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>adjudicate</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>Non-target descriptions at this and the previous timepoint, target response, sum change, guideline extract</t>
-        </is>
-      </c>
-      <c r="D6" s="66" t="inlineStr">
-        <is>
-          <t>{supports_unequivocal, magnitude_comment, confidence, rationale}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>P-MATCH-QUERY</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>match</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Candidate finding summary; historical queries for the subject</t>
-        </is>
-      </c>
-      <c r="D7" s="65" t="inlineStr">
-        <is>
-          <t>{matches:[{query_id, relation, confidence}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>P-ASSESS-ANSWER</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>assess</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>Query text, answer text, current values of the queried fields  (NEW at review)</t>
-        </is>
-      </c>
-      <c r="D8" s="66" t="inlineStr">
-        <is>
-          <t>{classification, confidence, rationale, quoted_span}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>P-NARRATE-FINDING</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>narrate</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Evidence object, rule metadata, message templates, guideline citation, indication context</t>
-        </is>
-      </c>
-      <c r="D9" s="65" t="inlineStr">
-        <is>
-          <t>{five narrative fields}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>P-INTAKE-PROTOCOL</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>summarise</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>Protocol and imaging charter text  (NEW at review, AC-11)</t>
-        </is>
-      </c>
-      <c r="D10" s="66" t="inlineStr">
-        <is>
-          <t>{checkpoints:[{parameter, value_found, page_ref, confidence}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Guardrails</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Numeric injection</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Numbers are never taken from model output. The template engine re-injects them from the evidence object and fails the render if a placeholder was dropped.</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Prompt injection defence</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>All site-authored text is wrapped in a labelled data envelope declared as data only. Output containing instruction-like content not originating in the template is rejected and the template fallback used. Suspicious site text is itself surfaced as an INFO finding.</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>G-03</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>No verdict authority</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Adjudication response schemas have no field able to create or delete a finding — only confidence, rationale and a downgrade flag where the rule permits it.</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>G-04</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>No critical suppression</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>The answer-assessment path cannot suppress a CRITICAL or MAJOR finding; it can only flag it as possibly justified for a human to close.</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>G-05</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>Determinism</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>temperature 0 and a fixed seed where supported. Narrative variation across runs is acceptable; verdict variation is impossible by construction.</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>G-06</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>Redaction</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>AMENDED v2.1.0. No data leaves the company network, so redaction is no longer an egress control. Subject identifiers are still pseudonymised in the prompt — not to protect against exfiltration, but so the model cannot anchor on a subject identifier as if it carried meaning.</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>G-07</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Evidence is deterministically summarised to fit the 32k prompt budget. Truncation is explicit and recorded, never silent.</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Adapters (amended v2.1.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Adapter</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>GLM v5.2</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>The only model</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Company-hosted, reached through the internal gateway. Transport, structured-output support and context limit are configuration confirmed against the actual deployment before Step 5 — they are not asserted here, because they were never verified against v5.2.</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Null</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>Verdict reference</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>Runs every LLM task through its deterministic template. Not a degraded mode but the definition of correct: GLM output is compared against it on every commit, and any difference in a deterministic verdict is a build failure.</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Capability negotiation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="130" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>strategy = select(glm_adapter.capabilities, task.requirements)
-  # capabilities are read from the deployed GLM v5.2 configuration,
-  # confirmed at Step 5 rather than assumed here
-  CONSTRAINED_JSON_SCHEMA -&gt; constrained decoding, single call
-  JSON_MODE               -&gt; JSON mode + schema validation
-  otherwise               -&gt; prompt-enforced JSON + schema validation
-on validation failure: one repair call carrying the validation error;
-on second failure: validation_status = FAILED, fall back to the deterministic template,
-log the event. The finding is still produced, with template text.</t>
-        </is>
-      </c>
-      <c r="B28" s="64" t="n"/>
-      <c r="C28" s="64" t="n"/>
-      <c r="D28" s="64" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A28:D28"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7133,6 +9137,32 @@
       </c>
       <c r="D27" s="14" t="inlineStr"/>
       <c r="E27" s="15" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Query_History</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Veeva query export, column by column</t>
+        </is>
+      </c>
+      <c r="C28" s="7">
+        <f>COUNTA(Query_History!A4:A57)</f>
+        <v/>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>TEA-CTR-004 — closes OI-09</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7175,6 +9205,435 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Model integration contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Prompt contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Output schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>P-ADJ-NONMEASURABLE</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>adjudicate</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Lesion organ, laterality, location text, description text, method, guideline extract</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>{is_non_measurable, category, confidence, rationale}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>P-ADJ-UNEQUIVOCAL</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>adjudicate</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Non-target descriptions at this and the previous timepoint, target response, sum change, guideline extract</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>{supports_unequivocal, magnitude_comment, confidence, rationale}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>P-MATCH-QUERY</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Candidate finding summary; historical queries for the subject</t>
+        </is>
+      </c>
+      <c r="D7" s="65" t="inlineStr">
+        <is>
+          <t>{matches:[{query_id, relation, confidence}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>P-ASSESS-ANSWER</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>assess</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Query text, answer text, current values of the queried fields  (NEW at review)</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>{classification, confidence, rationale, quoted_span}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>P-NARRATE-FINDING</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>narrate</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Evidence object, rule metadata, message templates, guideline citation, indication context</t>
+        </is>
+      </c>
+      <c r="D9" s="65" t="inlineStr">
+        <is>
+          <t>{five narrative fields}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>P-INTAKE-PROTOCOL</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>summarise</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Protocol and imaging charter text  (NEW at review, AC-11)</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>{checkpoints:[{parameter, value_found, page_ref, confidence}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Numeric injection</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Numbers are never taken from model output. The template engine re-injects them from the evidence object and fails the render if a placeholder was dropped.</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Prompt injection defence</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>All site-authored text is wrapped in a labelled data envelope declared as data only. Output containing instruction-like content not originating in the template is rejected and the template fallback used. Suspicious site text is itself surfaced as an INFO finding.</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>No verdict authority</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Adjudication response schemas have no field able to create or delete a finding — only confidence, rationale and a downgrade flag where the rule permits it.</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>No critical suppression</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>The answer-assessment path cannot suppress a CRITICAL or MAJOR finding; it can only flag it as possibly justified for a human to close.</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>G-05</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Determinism</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>temperature 0 and a fixed seed where supported. Narrative variation across runs is acceptable; verdict variation is impossible by construction.</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>G-06</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Redaction</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>AMENDED v2.1.0. No data leaves the company network, so redaction is no longer an egress control. Subject identifiers are still pseudonymised in the prompt — not to protect against exfiltration, but so the model cannot anchor on a subject identifier as if it carried meaning.</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Evidence is deterministically summarised to fit the 32k prompt budget. Truncation is explicit and recorded, never silent.</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Adapters (amended v2.1.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Adapter</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>GLM v5.2</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>The only model</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Company-hosted, reached through the internal gateway. Transport, structured-output support and context limit are configuration confirmed against the actual deployment before Step 5 — they are not asserted here, because they were never verified against v5.2.</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Verdict reference</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Runs every LLM task through its deterministic template. Not a degraded mode but the definition of correct: GLM output is compared against it on every commit, and any difference in a deterministic verdict is a build failure.</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Capability negotiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="130" customHeight="1">
+      <c r="A28" s="81" t="inlineStr">
+        <is>
+          <t>strategy = select(glm_adapter.capabilities, task.requirements)
+  # capabilities are read from the deployed GLM v5.2 configuration,
+  # confirmed at Step 5 rather than assumed here
+  CONSTRAINED_JSON_SCHEMA -&gt; constrained decoding, single call
+  JSON_MODE               -&gt; JSON mode + schema validation
+  otherwise               -&gt; prompt-enforced JSON + schema validation
+on validation failure: one repair call carrying the validation error;
+on second failure: validation_status = FAILED, fall back to the deterministic template,
+log the event. The finding is still produced, with template text.</t>
+        </is>
+      </c>
+      <c r="B28" s="64" t="n"/>
+      <c r="C28" s="64" t="n"/>
+      <c r="D28" s="64" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A28:D28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7475,7 +9934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7708,7 +10167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7836,7 +10295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8242,7 +10701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8742,7 +11201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/spec/TEA-SPEC-001_programming-specification.xlsx
+++ b/docs/spec/TEA-SPEC-001_programming-specification.xlsx
@@ -20,19 +20,20 @@
     <sheet name="GLM_Verification" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="SDTM_Requirements" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Query_History" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Query_Style" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Confidence_Model" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Query_Reconciliation" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Prioritisation" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Input_Contract" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Finding_Contract" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="LLM_Integration" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="API" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Testing" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Extensibility" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Open_Questions" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Traceability" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Review_Log" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Charter_Requirements" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Query_Style" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Confidence_Model" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Query_Reconciliation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Prioritisation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Input_Contract" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Finding_Contract" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="LLM_Integration" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="API" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Testing" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Extensibility" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Open_Questions" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Traceability" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Review_Log" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Definitions'!$A$3:$C$50</definedName>
@@ -265,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -488,6 +489,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -906,7 +911,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.6.0 — APPROVED, query history input contract</t>
+          <t>2.7.0 — APPROVED, imaging charter requirements</t>
         </is>
       </c>
     </row>
@@ -954,7 +959,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>v2.5.0, issued 2026-08-22</t>
+          <t>v2.6.0, issued 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4036,6 @@
       </c>
       <c r="G45" s="26" t="inlineStr"/>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -4259,7 +4263,6 @@
       <c r="E58" s="26" t="inlineStr"/>
       <c r="F58" s="26" t="inlineStr"/>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
@@ -6231,7 +6234,6 @@
           <t>0 — never appears</t>
         </is>
       </c>
-      <c r="D64" s="80" t="n"/>
       <c r="E64" s="72" t="inlineStr">
         <is>
           <t>Answer-assessment branch: P-ASSESS-ANSWER runs and TE-QM-002 / TE-QM-005 apply.</t>
@@ -6286,7 +6288,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D66" s="80" t="n"/>
       <c r="E66" s="72" t="inlineStr">
         <is>
           <t>The run fails before any rule executes, naming the column, the value and the affected Query IDs.</t>
@@ -6335,15 +6336,11 @@
           <t>2. Match header names leniently, values strictly.</t>
         </is>
       </c>
-      <c r="B71" s="80" t="n"/>
       <c r="C71" s="72" t="inlineStr">
         <is>
           <t>Header matching trims surrounding whitespace, collapses internal runs of spaces and ignores case. Everything after that — controlled values, date formats — is matched exactly.</t>
         </is>
       </c>
-      <c r="D71" s="80" t="n"/>
-      <c r="E71" s="80" t="n"/>
-      <c r="F71" s="80" t="n"/>
     </row>
     <row r="72" ht="41.5" customHeight="1">
       <c r="A72" s="68" t="inlineStr">
@@ -6363,15 +6360,11 @@
           <t>4. Fail the run on a missing R column, before any rule executes.</t>
         </is>
       </c>
-      <c r="B73" s="80" t="n"/>
       <c r="C73" s="72" t="inlineStr">
         <is>
           <t>Naming the column. A partial reconciliation is more dangerous than none, because a missing key produces false suppressions that look like a clean data set.</t>
         </is>
       </c>
-      <c r="D73" s="80" t="n"/>
-      <c r="E73" s="80" t="n"/>
-      <c r="F73" s="80" t="n"/>
     </row>
     <row r="74" ht="41.5" customHeight="1">
       <c r="A74" s="68" t="inlineStr">
@@ -6391,15 +6384,11 @@
           <t>6. Fail the run on an unrecognised value in a controlled column.</t>
         </is>
       </c>
-      <c r="B75" s="80" t="n"/>
       <c r="C75" s="72" t="inlineStr">
         <is>
           <t>Query Status, Manual Query, Restricted Query, Item Value Changed and Query Caused Data Change. An operational override exists for an urgent cut: it maps the unknown value to OPEN_UNRECOGNISED, suppresses nothing, and marks every affected finding unreconciled. The override is off by default and is recorded in the run provenance.</t>
         </is>
       </c>
-      <c r="D75" s="80" t="n"/>
-      <c r="E75" s="80" t="n"/>
-      <c r="F75" s="80" t="n"/>
     </row>
     <row r="76" ht="41.5" customHeight="1">
       <c r="A76" s="68" t="inlineStr">
@@ -6419,15 +6408,11 @@
           <t>8. Never parse the filename.</t>
         </is>
       </c>
-      <c r="B77" s="80" t="n"/>
       <c r="C77" s="72" t="inlineStr">
         <is>
           <t>The filename in this sample says A001-1001 while the Study column says A101-1001_TST5. The columns are the contract; the filename is not.</t>
         </is>
       </c>
-      <c r="D77" s="80" t="n"/>
-      <c r="E77" s="80" t="n"/>
-      <c r="F77" s="80" t="n"/>
     </row>
     <row r="78" ht="41.5" customHeight="1">
       <c r="A78" s="68" t="inlineStr">
@@ -6447,15 +6432,11 @@
           <t>10. Treat every text field as untrusted input (DP-07).</t>
         </is>
       </c>
-      <c r="B79" s="80" t="n"/>
       <c r="C79" s="72" t="inlineStr">
         <is>
           <t>Query text, comments and answers originate outside the trust boundary. They are passed to GLM v5.2 inside an explicit data envelope, with instruction-like content flagged, and they can never alter a deterministic verdict.</t>
         </is>
       </c>
-      <c r="D79" s="80" t="n"/>
-      <c r="E79" s="80" t="n"/>
-      <c r="F79" s="80" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -6504,14 +6485,11 @@
           <t>2. This export contains no site answers at all, so the answer path is unexercised.</t>
         </is>
       </c>
-      <c r="B84" s="80" t="n"/>
       <c r="C84" s="72" t="inlineStr">
         <is>
           <t>Latest Query Answer Text, Query Answered Date, Query Answered By, Answered By Role and Answered By Query Team are empty on all 69 rows, and no row carries status Answered. All 69 are system edit checks (Manual Query = No, Query Created By = System) and the 5 closed ones were auto-closed on data change. P-ASSESS-ANSWER, TE-QM-002 and TE-QM-005 — the LLM-adjudicated part of the query model — therefore have no example to build or test against. Two possibilities need separating: this listing does not populate the answer columns, or this study genuinely has no answered queries yet.</t>
         </is>
       </c>
-      <c r="D84" s="80" t="n"/>
-      <c r="E84" s="80" t="n"/>
       <c r="F84" s="72" t="inlineStr">
         <is>
           <t>ACTION — a second export containing manual, site-answered queries is needed before Step 3 can test the answer path.</t>
@@ -6541,14 +6519,11 @@
           <t>4. Part of TE-QM-002 becomes deterministic.</t>
         </is>
       </c>
-      <c r="B86" s="80" t="n"/>
       <c r="C86" s="72" t="inlineStr">
         <is>
           <t>Item Value Changed and Query Caused Data Change answer 'was the data actually corrected, and because of this query?' as a fact carried by the EDC, in a single cut. The approved design assumed this needed either LLM judgement (TE-QM-002) or a run-to-run diff (TE-QM-006). Under DP-01 the deterministic answer must win: where these columns are present, the correction fact is read, not inferred, and the model is asked only the question it is actually needed for — whether the site's reasoning justifies data that was NOT corrected. TE-QM-006 loses its two-run dependency entirely.</t>
         </is>
       </c>
-      <c r="D86" s="80" t="n"/>
-      <c r="E86" s="80" t="n"/>
       <c r="F86" s="72" t="inlineStr">
         <is>
           <t>CHANGE CONTROL — the rule pack is FROZEN at 2.0.0 and no rule text, message or base rate is changed here. This is recorded as a proposed implementation refinement, to be confirmed with evidence at the Step 3 gate and taken through rule change control at that point if it alters the stated logic of TE-QM-002 or TE-QM-006.</t>
@@ -6578,14 +6553,11 @@
           <t>6. The query export carries personal data in fields nobody would look for it in.</t>
         </is>
       </c>
-      <c r="B88" s="80" t="n"/>
       <c r="C88" s="72" t="inlineStr">
         <is>
           <t>Item Value Before Query and Item Value Now hold the raw field values, and in this sample three of the four are birth years (2008 → 1989, 1910 → 1951, 1906 → 1953). The file also carries site and subject identifiers throughout, and is marked RESTRICTED in its filename while Restricted Query reads No on every row. Guardrail G-06 was scoped for tumour data. It is extended to the query-history block: value_before and value_after are redacted before any prompt is assembled, and the file is handled at the same sensitivity as the clinical data set.</t>
         </is>
       </c>
-      <c r="D88" s="80" t="n"/>
-      <c r="E88" s="80" t="n"/>
       <c r="F88" s="72" t="inlineStr">
         <is>
           <t>CLOSED by this contract — G-06 extended, and the Restricted Query flag alone is not treated as sufficient.</t>
@@ -6658,9 +6630,9 @@
     <mergeCell ref="C72:F72"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A70:B70"/>
+    <mergeCell ref="B93:F93"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="C64:D64"/>
-    <mergeCell ref="B93:F93"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="A2:F2"/>
@@ -6708,6 +6680,1391 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="84" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Imaging charter requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="67" t="inlineStr">
+        <is>
+          <t>TEA-CTR-005. What the agent needs from the imaging charter — the third configuration input, alongside the protocol summary and the SDTM delivery. The charter is authoritative for how lesions are measured and read; the protocol is authoritative for what the study does. Written against the general structure of a BICR charter, since real charters cannot leave the company. The extract that satisfies it is APPLY slot A-08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Charter parameter</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Configuration field</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>R/C/O</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Also in the protocol?</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>What the agent uses it for</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>If absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="68" t="inlineStr">
+        <is>
+          <t>Response criteria and version</t>
+        </is>
+      </c>
+      <c r="B4" s="68" t="inlineStr">
+        <is>
+          <t>criteria_version</t>
+        </is>
+      </c>
+      <c r="C4" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D4" s="69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Selects the guideline profile: RECIST 1.1, iRECIST, or both with iRECIST scoped to named arms. Everything else the agent derives follows from this.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Cannot run. There is no safe default — assuming RECIST 1.1 for an iRECIST study produces wrong progression calls, confidently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>Modifications to the published criteria</t>
+        </is>
+      </c>
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>criteria_modifications</t>
+        </is>
+      </c>
+      <c r="C5" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D5" s="76" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E5" s="72" t="inlineStr">
+        <is>
+          <t>A charter that alters a threshold, a lesion cap or a progression definition has created a modified criteria set. The agent must be told explicitly, because its derivations otherwise implement the published version and every comparison is against the wrong standard.</t>
+        </is>
+      </c>
+      <c r="F5" s="72" t="inlineStr">
+        <is>
+          <t>Assumed none. This is the most dangerous silent assumption in the whole configuration: an unrecorded modification makes the agent disagree with the reader on every affected timepoint, and the agent will look wrong when it is the configuration that is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="68" t="inlineStr">
+        <is>
+          <t>Reader paradigm</t>
+        </is>
+      </c>
+      <c r="B6" s="68" t="inlineStr">
+        <is>
+          <t>reader_paradigm</t>
+        </is>
+      </c>
+      <c r="C6" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D6" s="75" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Single reader, double read with adjudication, or investigator only. Determines how many response streams exist and what a disagreement between them means.</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Streams merge. Every lesion and every response duplicates, and the agent reports discrepancies that are really two readers doing their job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>Evaluator streams carried in the data</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>evaluator_streams</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D7" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E7" s="72" t="inlineStr">
+        <is>
+          <t>Which of investigator and independent review reach the agent, and how they appear in TUEVAL and RSEVAL. Each stream derives independently and is never compared across streams by a rule.</t>
+        </is>
+      </c>
+      <c r="F7" s="72" t="inlineStr">
+        <is>
+          <t>Cannot separate readers. See TE-RS-020.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t>Maximum target lesions in total</t>
+        </is>
+      </c>
+      <c r="B8" s="68" t="inlineStr">
+        <is>
+          <t>max_target_lesions</t>
+        </is>
+      </c>
+      <c r="C8" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D8" s="69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>TE-BL-002 and the target-selection family. RECIST 1.1 default is 5.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to the guideline default of 5, recorded as a default rather than a source value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>Maximum target lesions per organ</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>max_target_per_organ</t>
+        </is>
+      </c>
+      <c r="C9" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D9" s="76" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E9" s="72" t="inlineStr">
+        <is>
+          <t>TE-BL-002, TE-IR-006. RECIST 1.1 default is 2.</t>
+        </is>
+      </c>
+      <c r="F9" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to 2, recorded as a default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>Lesion selection principle</t>
+        </is>
+      </c>
+      <c r="B10" s="68" t="inlineStr">
+        <is>
+          <t>lesion_selection_rule</t>
+        </is>
+      </c>
+      <c r="C10" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Reproducible, measurable, representative of overall disease burden. Used by the model when adjudicating whether a selection was defensible, not by any deterministic rule.</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>The adjudication prompt loses its standard and falls back to the guideline wording.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>Lesions that split or coalesce</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>split_merge_policy</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E11" s="72" t="inlineStr">
+        <is>
+          <t>How a target lesion that separates into two, or two that merge, is measured and counted thereafter. RECIST 1.1 is close to silent on this; charters usually are not.</t>
+        </is>
+      </c>
+      <c r="F11" s="72" t="inlineStr">
+        <is>
+          <t>The lesion-count and sum rules see an unexplained change in lesion number and raise a structural finding that is actually correct reader behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="68" t="inlineStr">
+        <is>
+          <t>Previously irradiated lesions</t>
+        </is>
+      </c>
+      <c r="B12" s="68" t="inlineStr">
+        <is>
+          <t>irradiated_lesion_policy</t>
+        </is>
+      </c>
+      <c r="C12" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="75" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Whether a lesion in a previously irradiated field may be selected as target. Feeds the XD rules that look at radiotherapy history.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>TE-XD rules on prior radiotherapy cannot judge selection and report NOT_EVALUATED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>Minimum measurable size, non-nodal</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>min_measurable_mm</t>
+        </is>
+      </c>
+      <c r="C13" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E13" s="72" t="inlineStr">
+        <is>
+          <t>TE-BL-004, TE-BL-014. The threshold below which a lesion is not measurable. RECIST 1.1 default is 10 mm by CT.</t>
+        </is>
+      </c>
+      <c r="F13" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to 10 mm, which is wrong for any study imaging at a coarser slice thickness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t>Minimum nodal short axis for target</t>
+        </is>
+      </c>
+      <c r="B14" s="68" t="inlineStr">
+        <is>
+          <t>min_nodal_target_mm</t>
+        </is>
+      </c>
+      <c r="C14" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D14" s="75" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>TE-BL-005 and the nodal family. RECIST 1.1 default is 15 mm short axis.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to 15 mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>Nodal normal threshold</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>nodal_normal_mm</t>
+        </is>
+      </c>
+      <c r="C15" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D15" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E15" s="72" t="inlineStr">
+        <is>
+          <t>A node under this short axis is normal, which is what complete response of a nodal target requires. RECIST 1.1 default is 10 mm.</t>
+        </is>
+      </c>
+      <c r="F15" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to 10 mm. Complete-response checks are unreliable if the charter set a different threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>Maximum slice thickness</t>
+        </is>
+      </c>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>slice_thickness_max_mm</t>
+        </is>
+      </c>
+      <c r="C16" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D16" s="77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Measurability is a function of acquisition: the minimum measurable lesion is conventionally twice the slice thickness. This is why measurability belongs to the charter and not the protocol.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>The measurability threshold cannot be checked against acquisition. TE-BL-006 and TE-BL-015 deactivate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>Measurement axis by lesion type</t>
+        </is>
+      </c>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>measurement_axis_rule</t>
+        </is>
+      </c>
+      <c r="C17" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E17" s="72" t="inlineStr">
+        <is>
+          <t>Longest diameter for non-nodal, short axis for nodal. Resolves TRTESTCD when the EDC does not collect the axis type explicitly. See TE-ST-003.</t>
+        </is>
+      </c>
+      <c r="F17" s="72" t="inlineStr">
+        <is>
+          <t>Cannot resolve the axis. A node measured as a longest diameter silently breaks every nodal threshold — wrong answers, not missing ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="68" t="inlineStr">
+        <is>
+          <t>Measurement precision and rounding</t>
+        </is>
+      </c>
+      <c r="B18" s="68" t="inlineStr">
+        <is>
+          <t>measurement_precision</t>
+        </is>
+      </c>
+      <c r="C18" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" s="77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>How many decimal places are recorded and what rounding the reader applies. The agent uses it as the tolerance below which its recomputed sum is not called a discrepancy.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Tolerance falls back to a conservative default. Rounding differences surface as low-confidence findings — noise rather than error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>Non-measurable disease categories</t>
+        </is>
+      </c>
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>non_measurable_categories</t>
+        </is>
+      </c>
+      <c r="C19" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D19" s="71" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E19" s="72" t="inlineStr">
+        <is>
+          <t>Effusions, ascites, leptomeningeal disease, bone lesions without a soft-tissue component. Drives the non-target family and TE-RS-021.</t>
+        </is>
+      </c>
+      <c r="F19" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to the RECIST 1.1 list, which most charters restate unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="68" t="inlineStr">
+        <is>
+          <t>Bone lesion policy</t>
+        </is>
+      </c>
+      <c r="B20" s="68" t="inlineStr">
+        <is>
+          <t>bone_lesion_policy</t>
+        </is>
+      </c>
+      <c r="C20" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" s="77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Whether a bone lesion with an identifiable soft-tissue component may be a target.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to the guideline default; charter-specific restrictions go unenforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="70" t="inlineStr">
+        <is>
+          <t>Modalities permitted</t>
+        </is>
+      </c>
+      <c r="B21" s="70" t="inlineStr">
+        <is>
+          <t>modalities_allowed</t>
+        </is>
+      </c>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D21" s="71" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E21" s="72" t="inlineStr">
+        <is>
+          <t>TE-BL-003, TE-XD-008. Which of CT, MRI, PET-CT and clinical measurement may be used, and for which lesion types.</t>
+        </is>
+      </c>
+      <c r="F21" s="72" t="inlineStr">
+        <is>
+          <t>Method rules deactivate; a lesion measured by an unpermitted modality is not detected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>Modality consistency requirement</t>
+        </is>
+      </c>
+      <c r="B22" s="68" t="inlineStr">
+        <is>
+          <t>modality_consistency_rule</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" s="77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Whether a lesion must be followed by the same modality throughout. TE-BL-014 and TE-FU-013 depend on it.</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Modality changes mid-study are not flagged, though they are a common and consequential source of apparent change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="70" t="inlineStr">
+        <is>
+          <t>Contrast requirement</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
+        <is>
+          <t>contrast_requirement</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E23" s="72" t="inlineStr">
+        <is>
+          <t>Whether contrast is required, and how a non-contrast study is handled.</t>
+        </is>
+      </c>
+      <c r="F23" s="72" t="inlineStr">
+        <is>
+          <t>Contrast findings deactivate; a non-contrast scan reads as equivalent to a contrast one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="68" t="inlineStr">
+        <is>
+          <t>Anatomical coverage per timepoint</t>
+        </is>
+      </c>
+      <c r="B24" s="68" t="inlineStr">
+        <is>
+          <t>required_regions</t>
+        </is>
+      </c>
+      <c r="C24" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D24" s="75" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Which regions must be imaged at each assessment. This is what separates a genuinely missing measurement from a region that was never required.</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>TE-FU-002 cannot tell an omission from an intended absence and queries scans that were never in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="70" t="inlineStr">
+        <is>
+          <t>Brain imaging policy</t>
+        </is>
+      </c>
+      <c r="B25" s="70" t="inlineStr">
+        <is>
+          <t>brain_imaging_policy</t>
+        </is>
+      </c>
+      <c r="C25" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D25" s="76" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E25" s="72" t="inlineStr">
+        <is>
+          <t>Baseline requirement and whether follow-up is scheduled or clinically indicated. Frequently a protocol-versus-charter conflict.</t>
+        </is>
+      </c>
+      <c r="F25" s="72" t="inlineStr">
+        <is>
+          <t>Brain lesion handling falls back to the general rules, which may over-query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="68" t="inlineStr">
+        <is>
+          <t>Partial response threshold</t>
+        </is>
+      </c>
+      <c r="B26" s="68" t="inlineStr">
+        <is>
+          <t>pr_percent_decrease</t>
+        </is>
+      </c>
+      <c r="C26" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D26" s="77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>The derivation engine. RECIST 1.1 default is a 30% decrease from baseline.</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="70" t="inlineStr">
+        <is>
+          <t>Progression threshold</t>
+        </is>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
+          <t>pd_percent_increase</t>
+        </is>
+      </c>
+      <c r="C27" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D27" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E27" s="72" t="inlineStr">
+        <is>
+          <t>The derivation engine. RECIST 1.1 default is a 20% increase from nadir.</t>
+        </is>
+      </c>
+      <c r="F27" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to 20%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="68" t="inlineStr">
+        <is>
+          <t>Progression absolute minimum</t>
+        </is>
+      </c>
+      <c r="B28" s="68" t="inlineStr">
+        <is>
+          <t>pd_absolute_min_mm</t>
+        </is>
+      </c>
+      <c r="C28" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D28" s="77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>The 5 mm absolute increase that must accompany the 20%. Omitting it is a classic derivation error, and one of the highest-yield checks in the pack.</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Falls back to 5 mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="70" t="inlineStr">
+        <is>
+          <t>Complete response nodal threshold</t>
+        </is>
+      </c>
+      <c r="B29" s="70" t="inlineStr">
+        <is>
+          <t>cr_nodal_short_axis_mm</t>
+        </is>
+      </c>
+      <c r="C29" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D29" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E29" s="72" t="inlineStr">
+        <is>
+          <t>Nodal targets must fall below this short axis for complete response. Default 10 mm.</t>
+        </is>
+      </c>
+      <c r="F29" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to 10 mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="68" t="inlineStr">
+        <is>
+          <t>New lesion standard</t>
+        </is>
+      </c>
+      <c r="B30" s="68" t="inlineStr">
+        <is>
+          <t>new_lesion_standard</t>
+        </is>
+      </c>
+      <c r="C30" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D30" s="75" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>The wording the charter uses for an unequivocal new lesion, and what happens to an equivocal finding. This is the standard the model is held to when it adjudicates a new-lesion judgement — it is quoted into the prompt, not paraphrased.</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>The adjudication prompt falls back to the guideline wording, and the model is judged against a standard the readers were not given.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="70" t="inlineStr">
+        <is>
+          <t>Non-target progression standard</t>
+        </is>
+      </c>
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>nt_progression_standard</t>
+        </is>
+      </c>
+      <c r="C31" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D31" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E31" s="72" t="inlineStr">
+        <is>
+          <t>The wording for unequivocal non-target progression. Same treatment as the new-lesion standard: it is a declared judgement rule, quoted verbatim.</t>
+        </is>
+      </c>
+      <c r="F31" s="72" t="inlineStr">
+        <is>
+          <t>Falls back to the guideline wording.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="68" t="inlineStr">
+        <is>
+          <t>Response confirmation requirement</t>
+        </is>
+      </c>
+      <c r="B32" s="68" t="inlineStr">
+        <is>
+          <t>confirmation_required</t>
+        </is>
+      </c>
+      <c r="C32" s="69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" s="69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Whether complete and partial response require confirmation, and the minimum interval. The parameter most likely to differ between the protocol and the charter.</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Assumed required at 4 weeks. If the study does not require confirmation this produces a systematic false-finding stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="70" t="inlineStr">
+        <is>
+          <t>iRECIST confirmation window</t>
+        </is>
+      </c>
+      <c r="B33" s="70" t="inlineStr">
+        <is>
+          <t>irecist_confirm_window_weeks</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D33" s="76" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E33" s="72" t="inlineStr">
+        <is>
+          <t>The window in which iUPD must be reassessed to establish or refute iCPD. Typically 4 to 8 weeks. Drives the iRECIST timing rules.</t>
+        </is>
+      </c>
+      <c r="F33" s="72" t="inlineStr">
+        <is>
+          <t>iRECIST timing rules deactivate and report NOT_EVALUATED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="68" t="inlineStr">
+        <is>
+          <t>Assessment schedule and window</t>
+        </is>
+      </c>
+      <c r="B34" s="68" t="inlineStr">
+        <is>
+          <t>timepoint_windows_days</t>
+        </is>
+      </c>
+      <c r="C34" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D34" s="69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>The nominal interval and the permitted deviation. Usually the protocol's, sometimes restated by the charter.</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Assessment-window rules deactivate. Unscheduled and out-of-window visits are not distinguished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="70" t="inlineStr">
+        <is>
+          <t>Non-evaluable timepoint rules</t>
+        </is>
+      </c>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>non_evaluable_rules</t>
+        </is>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" s="71" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="E35" s="72" t="inlineStr">
+        <is>
+          <t>When a timepoint is not evaluable, and how a partially imaged timepoint is scored. Determines whether a gap is a finding or an expected outcome.</t>
+        </is>
+      </c>
+      <c r="F35" s="72" t="inlineStr">
+        <is>
+          <t>Every gap becomes a finding. This is the single largest source of avoidable query volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="68" t="inlineStr">
+        <is>
+          <t>Image transfer and read lag</t>
+        </is>
+      </c>
+      <c r="B36" s="68" t="inlineStr">
+        <is>
+          <t>read_lag_days</t>
+        </is>
+      </c>
+      <c r="C36" s="75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" s="77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>The expected interval between acquisition and an available central read. The agent uses it to suppress findings about a read that cannot have happened yet at this data cut.</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>The agent queries missing central responses for scans that are still within the normal reading lag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="70" t="inlineStr">
+        <is>
+          <t>Adjudication trigger</t>
+        </is>
+      </c>
+      <c r="B37" s="70" t="inlineStr">
+        <is>
+          <t>adjudication_trigger</t>
+        </is>
+      </c>
+      <c r="C37" s="73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D37" s="78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E37" s="72" t="inlineStr">
+        <is>
+          <t>What sends a timepoint to the adjudicator. An adjudicated timepoint is evidence that the call was genuinely hard; the agent weights its confidence down rather than re-litigating it.</t>
+        </is>
+      </c>
+      <c r="F37" s="72" t="inlineStr">
+        <is>
+          <t>Adjudicated timepoints are treated like any other. Findings against them carry unwarranted confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="79" t="inlineStr">
+        <is>
+          <t>R = required; without it the run stops or a named derivation is wrong.   C = conditional; its absence deactivates a named behaviour, which is reported.   O = optional.   "Also in the protocol?" YES means both documents routinely state it and can disagree — see the conflict section below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>When the protocol and the charter disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="79" t="inlineStr">
+        <is>
+          <t>Eight of the 34 parameters are routinely stated in both documents and another ten sometimes are, so up to half can disagree. TEA-BND-001 law L6: a conflict is a finding, not a choice. Silently preferring either document buries a real protocol-deviation risk in a configuration file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>How they typically disagree</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Why it cannot be resolved automatically</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="79" customHeight="1">
+      <c r="A44" s="68" t="inlineStr">
+        <is>
+          <t>Confirmation interval</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Protocol says 4 weeks; charter says 28 days from the first response scan.</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Usually the same thing stated differently, but not always — 4 weeks from the scan and 4 weeks from the response record differ when the read lags. Report, and let the study team say which.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="91.5" customHeight="1">
+      <c r="A45" s="70" t="inlineStr">
+        <is>
+          <t>Target lesion cap</t>
+        </is>
+      </c>
+      <c r="B45" s="80" t="n"/>
+      <c r="C45" s="72" t="inlineStr">
+        <is>
+          <t>Protocol restates RECIST 1.1 at 5; charter tightens to 3 for a specific tumour type.</t>
+        </is>
+      </c>
+      <c r="D45" s="80" t="n"/>
+      <c r="E45" s="72" t="inlineStr">
+        <is>
+          <t>The charter is normally authoritative for reading, but the protocol drives the endpoint definition. This is exactly the case where guessing is wrong — report it.</t>
+        </is>
+      </c>
+      <c r="F45" s="80" t="n"/>
+    </row>
+    <row r="46" ht="91.5" customHeight="1">
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t>Measurability threshold</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Protocol says 10 mm; charter says twice the slice thickness, and the study images at 7 mm.</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>The charter's rule is stricter and is the one the readers followed. The agent must use 14 mm, but only after the conflict has been seen and decided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="91.5" customHeight="1">
+      <c r="A47" s="70" t="inlineStr">
+        <is>
+          <t>Brain imaging</t>
+        </is>
+      </c>
+      <c r="B47" s="80" t="n"/>
+      <c r="C47" s="72" t="inlineStr">
+        <is>
+          <t>Protocol requires baseline brain MRI for all; charter says when clinically indicated.</t>
+        </is>
+      </c>
+      <c r="D47" s="80" t="n"/>
+      <c r="E47" s="72" t="inlineStr">
+        <is>
+          <t>Changes whether a missing baseline brain scan is a protocol deviation or expected. Both readings produce findings; only one is right.</t>
+        </is>
+      </c>
+      <c r="F47" s="80" t="n"/>
+    </row>
+    <row r="48" ht="91.5" customHeight="1">
+      <c r="A48" s="68" t="inlineStr">
+        <is>
+          <t>iRECIST scope</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Protocol applies iRECIST to the immunotherapy arm; charter applies it to all subjects.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Determines which response set the agent derives per subject. Getting this wrong misclassifies every progression in the comparator arm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>How a parameter is resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>1.  The charter extract (A-08) and the protocol summary (A-07) are both read by AC-11, independently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>2.  Every parameter records which document it came from, and the section within it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>3.  Where both documents supply a parameter and the values agree, the parameter is set and the agreement is recorded — that agreement is itself evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>4.  Where both supply it and the values disagree, the parameter is left UNRESOLVED. The run does not start with an unresolved parameter that a live rule depends on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>5.  The conflict is presented on screen S7 with both values, both citations, and the rules that depend on it. The study team decides; the decision and the person are recorded in the run provenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>6.  Where only one document supplies it, that value is used and the single source is recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>7.  Where neither does, the guideline default applies and is recorded AS a default — never as a source value. The distinction matters at audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="41.5" customHeight="1">
+      <c r="A59" s="82" t="inlineStr">
+        <is>
+          <t>NOT A RULE CHANGE. The conflict check is a configuration-time behaviour of AC-11 and AC-02, not a review point. The rule pack stays FROZEN at 2.0.0 and no TE- rule is added, amended or renumbered by this sheet. If experience at Step 3 shows the conflict check belongs in the rule pack, that goes through rule change control at that point.</t>
+        </is>
+      </c>
+      <c r="B59" s="83" t="n"/>
+      <c r="C59" s="83" t="n"/>
+      <c r="D59" s="83" t="n"/>
+      <c r="E59" s="83" t="n"/>
+      <c r="F59" s="83" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="E47:F47"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7026,7 +8383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7352,7 +8709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7494,7 +8851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7574,13 +8931,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7970,6 +9327,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -8002,6 +9360,33 @@
       <c r="B22" s="7" t="inlineStr">
         <is>
           <t>•  Dates are ISO-8601; partial dates stay partial and rules needing full precision declare themselves not evaluable for that record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>charter_config</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>criteria_version, criteria_modifications, reader_paradigm, measurability and response thresholds, non-evaluable rules, source citations</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>NEW v2.7.0. The imaging charter extract. See Charter_Requirements (TEA-CTR-005). Produced in the company as APPLY slot A-08. Where it and protocol_summary disagree, AC-11 reports the conflict and leaves the parameter unresolved rather than choosing.</t>
         </is>
       </c>
     </row>
@@ -8009,550 +9394,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Finding output contract</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>TEA-CTR-002. The agent's unit of output, consumed by the web application and exports.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>finding_id, run_id</t>
-        </is>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Identity of this record in this run.</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>rule_id, rule_version</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Which rule fired, at what version.</t>
-        </is>
-      </c>
-      <c r="D5" s="26" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>dedupe_key</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>sha256 of study, subject, rule, assessment scope, lesion scope, rule major version. Stable across runs and across PATCH/MINOR rule changes.</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>subject_id, site_id, assessment_ids, lesion_ids</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>refs</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>What the finding is about.</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>severity, original_severity</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>CRITICAL | MAJOR | MINOR | INFO. original_severity is set when the reconciler escalated.</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>determination_mode</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>DETERMINISTIC | LLM_ADJUDICATED | HYBRID.</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>confidence_rate</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>0.02 – 0.99. Probability the finding is a correct query. Displayed as xx.x%.</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>confidence_factors</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>The five contributing factors, so a surprising score can be explained.</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>SITE | STUDY_TEAM. STUDY_TEAM findings are never issued as site queries.</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>evidence.observed / expected</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>Values as collected versus as derived. Authoritative; the narrative is not.</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>evidence.records</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>object[]</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Pointers to the exact source records, with form and field.</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>evidence.derivation_trace</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>object[]</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>Ordered derivation steps with inputs and outputs; drives the UI evidence panel.</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>narrative.review_point_text</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Element 1 — what review point was checked.</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>narrative.issue_text</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>Element 2 — what the issue is, on which data.</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>narrative.reason_text</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Element 3 — why it is an issue; current versus expected.</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>narrative.suggested_query_text</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>Element 4 — draft query, editable before issuance.</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>narrative.additional_info_text</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Element 5 — review tips and guideline elaboration.</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>narrative.placeholders_verified</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>True when every numeric placeholder was re-injected from evidence after generation.</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>guideline_citations</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>object[]</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Knowledge-base entry id and clause.</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>query_link_status</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>NEW | DUPLICATE_OPEN | ANSWERED_RESOLVED | ANSWERED_UNRESOLVED | JUSTIFIED_BY_ANSWER | RECURRENT.</t>
-        </is>
-      </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>AMENDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>answer_assessment</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Classification, confidence and quoted answer where a prior query was assessed.</t>
-        </is>
-      </c>
-      <c r="D24" s="31" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>linked_query_ids, match_basis</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>refs / enum</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>EXACT | STRUCTURAL | SEMANTIC.</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>priority_score, priority_components</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>number / object</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Inspectable ranking.</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>root_finding_id, related_finding_ids</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>refs</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>Cascade grouping.</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>disposition + reason code, by, datetime</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>enum / string</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Reviewer action, feeding the confidence model.</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>provenance</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
-        <is>
-          <t>Engine, rule pack, prompt, model, guideline and config versions; dataset snapshot hash.</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8564,7 +9405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9161,6 +10002,32 @@
       <c r="E28" s="7" t="inlineStr">
         <is>
           <t>TEA-CTR-004 — closes OI-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Charter_Requirements</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>What the agent needs from the imaging charter</t>
+        </is>
+      </c>
+      <c r="C29" s="7">
+        <f>COUNTA(Charter_Requirements!A4:A37)</f>
+        <v/>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>TEA-CTR-005 — feeds A-08</t>
         </is>
       </c>
     </row>
@@ -9205,6 +10072,550 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Finding output contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>TEA-CTR-002. The agent's unit of output, consumed by the web application and exports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>finding_id, run_id</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Identity of this record in this run.</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>rule_id, rule_version</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Which rule fired, at what version.</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>dedupe_key</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>sha256 of study, subject, rule, assessment scope, lesion scope, rule major version. Stable across runs and across PATCH/MINOR rule changes.</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>subject_id, site_id, assessment_ids, lesion_ids</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>refs</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>What the finding is about.</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>severity, original_severity</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>CRITICAL | MAJOR | MINOR | INFO. original_severity is set when the reconciler escalated.</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>determination_mode</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>DETERMINISTIC | LLM_ADJUDICATED | HYBRID.</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>confidence_rate</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>0.02 – 0.99. Probability the finding is a correct query. Displayed as xx.x%.</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>confidence_factors</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>The five contributing factors, so a surprising score can be explained.</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>audience</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>SITE | STUDY_TEAM. STUDY_TEAM findings are never issued as site queries.</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>evidence.observed / expected</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Values as collected versus as derived. Authoritative; the narrative is not.</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>evidence.records</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>object[]</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Pointers to the exact source records, with form and field.</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>evidence.derivation_trace</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>object[]</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Ordered derivation steps with inputs and outputs; drives the UI evidence panel.</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>narrative.review_point_text</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Element 1 — what review point was checked.</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>narrative.issue_text</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Element 2 — what the issue is, on which data.</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>narrative.reason_text</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Element 3 — why it is an issue; current versus expected.</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>narrative.suggested_query_text</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Element 4 — draft query, editable before issuance.</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>narrative.additional_info_text</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Element 5 — review tips and guideline elaboration.</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>narrative.placeholders_verified</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>True when every numeric placeholder was re-injected from evidence after generation.</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>guideline_citations</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>object[]</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Knowledge-base entry id and clause.</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>query_link_status</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>NEW | DUPLICATE_OPEN | ANSWERED_RESOLVED | ANSWERED_UNRESOLVED | JUSTIFIED_BY_ANSWER | RECURRENT.</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>AMENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>answer_assessment</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Classification, confidence and quoted answer where a prior query was assessed.</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>linked_query_ids, match_basis</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>refs / enum</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>EXACT | STRUCTURAL | SEMANTIC.</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>priority_score, priority_components</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>number / object</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Inspectable ranking.</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>root_finding_id, related_finding_ids</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>refs</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Cascade grouping.</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>disposition + reason code, by, datetime</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>enum / string</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Reviewer action, feeding the confidence model.</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Engine, rule pack, prompt, model, guideline and config versions; dataset snapshot hash.</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9628,7 +11039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9934,7 +11345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10167,7 +11578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10295,7 +11706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10701,7 +12112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11201,7 +12612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
